--- a/Result/checksun_type/醫療院所.xlsx
+++ b/Result/checksun_type/醫療院所.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>27.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>27.32</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>28.96</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>6377966.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>6176987.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>6176987.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5819335.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7057711.28</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>7057711.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>318810.7876168946</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>6377966</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>6377966.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>26.65</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>27.34</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>29</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>14065095.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>5502534.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>5502534.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5577139.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7141675.4</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7141675.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>354777.3309102692</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>14065095</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>14065095.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>26.32</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>27.38</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>29.06</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2914289.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3848013.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3848013.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>4769960.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7033263.38</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7033263.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-430133.4762031334</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2914289</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2914289.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>26.41</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>27.52</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>29.16</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>29.16</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>4874674.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4326733.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>4326733.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5162658.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7253837.46</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7253837.46</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-341343.5050721681</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>4874674</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4874674.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>26.76</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>29.27</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>29.27</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>2652914.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4882698.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>4882698.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5090432.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7327974.3</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>7327974.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-412351.0997039247</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>2652914</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2652914.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>26.91</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>27.88</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>29.36</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>29.36</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3005699.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>5461683.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>5461683</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>5213400.7</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>7669422.94</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>7669422.94</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-261017.9813312953</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3005699</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3005699.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>27.11</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>29.48</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>29.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>5792491.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>5651744.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>5651744.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>5390737.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>7832741.84</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>7832741.84</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-73304.13432285003</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>5792491</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5792491.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>27.24</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>29.6</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>5307889.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>5691908.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>5691908</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>5278991.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>8214914.5</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>8214914.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-101108.3480849694</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>5307889</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>5307889.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>27.29</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>28.36</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>29.72</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>29.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>7654500.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>5998583.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>5998583.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>4953026.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>8631788.52</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>8631788.52</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-85295.99817067571</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>7654500</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>7654500.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>27.27</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>28.44</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>29.8</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>5547836.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>5298166.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>5298166.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>4494096.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>8670075.9</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>8670075.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-311083.2483584471</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>5547836</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>5547836.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>27.34</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>28.52</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>29.89</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>29.89</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>3956007.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4965118.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4965118.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>4940124.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>8893843.2</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>8893843.199999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-396812.3468996035</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>3956007</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>3956007.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>18.99</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>18.93</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>20.39</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>20.39</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>19.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-31.05550327662563</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>19</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>19.09</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>18.93</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>20.47</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>20.47</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>302.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>0</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-25.31309603656888</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>302</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>302.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>19.34</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>20.54</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>20.54</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>19.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>0</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-46.5270465494675</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>19</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>19.43</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>20.56</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>20.56</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>62.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>0</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-44.84958133398455</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>62</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>19.37</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>19.05</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>20.59</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>20.59</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>0</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>0</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-44.09605112284888</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>0</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>19.2</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>19.07</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>20.6</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>156.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>114.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>114.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-44.09605112284888</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>156</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>18.97</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>19.08</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>20.62</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>20.62</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>59.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>130.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>130.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-52.85692266478695</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>59</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>18.75</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>20.63</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>20.63</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>79.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>130.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-53.09184905809897</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>79</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>18.65</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>20.64</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>151.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>0</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-53.67417786789835</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>151</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>18.69</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>20.68</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>126.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>0</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>0</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-60.3034269580439</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>126</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>18.68</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>19.22</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>20.7</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>237.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>0</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>0</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-64.94151755260745</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>237</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>237.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>29.28</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>29.07</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>29.12</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>29.12</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>375.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>458.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>458.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>468.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>513.9</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>513.9</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>9.717983920189226</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>375</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>375.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>29.2</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>29.14</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>29.14</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>628.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>553.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>553.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>481.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>527.1</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>527.1</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>20.70602374197421</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>628</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>628.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>29.13</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>29.15</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>374.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>536.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>536.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>452.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>546.88</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>546.88</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>8.556579782310848</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>374</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>374.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>29.03</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>29.02</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>29.16</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>29.16</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>496.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>522.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>522</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>437.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>556.4</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>556.4</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>18.10892484770926</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>496</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>496.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>29.02</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>29.18</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>29</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>29.18</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>420.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>511.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>511.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>405.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>569.6</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>569.6</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>18.03695619657452</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>420</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>420.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>29.01</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>28.99</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>29.19</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>29.19</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>850.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>479.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>479.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>374.1</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>594.44</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>594.4400000000001</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>25.4328239736472</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>850</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>29.14</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>29.2</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>544.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>409.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>409.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>306.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>590.14</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>590.14</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-10.98139434387917</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>544</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>544.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>29.21</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>29.02</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>29.2</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>300.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>368.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>368.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>284.8</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>586.4</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>586.4</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-29.82379928520692</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>300</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>29.34</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>29.04</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>29.19</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>29.19</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>443.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>353.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>353.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>282.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>598.22</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>598.22</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-29.53352779834626</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>443</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>443.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>29.28</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>29.02</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>29.18</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>29.18</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>259.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>299.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>299.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>301.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>592.04</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>592.04</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-43.38551396717583</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>259</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>259.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>29.24</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>28.99</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>29.18</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>29.18</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>501.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>269.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>269</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>337.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>597.34</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>597.34</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-41.91029728096174</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>501</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>501.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>23.06</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>23.79</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>24.49</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>24.49</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>1076.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>799.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>799.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>923.3</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>113.8727451425915</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>1076</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>1076.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>22.76</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>23.88</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>24.52</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>24.52</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>946.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>678.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>678.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>834.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>0</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>109.001937748681</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>946</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>946.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>22.68</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>23.97</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>24.56</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>24.56</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>733.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1382.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1382.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>743.1</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>0</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>112.0792865520704</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>733</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>733.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>22.86</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>24.06</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>24.61</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>24.61</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>862.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1271.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1271.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>705.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>0</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>135.2940960371956</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>862</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>862.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>23.09</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>24.19</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>24.66</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>24.66</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>379.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1118.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1118.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>631.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>0</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>149.8047490146175</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>379</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>379.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>23.39</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>24.3</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>24.72</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>24.72</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>473.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1047.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1047.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>627.5</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>0</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>216.9340836604125</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>473</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>473.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>23.76</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>24.46</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>24.8</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>4465.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>991.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>991.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>582.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>0</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>295.0140587379619</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>4465</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>4465.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>24.04</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>24.85</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>179.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>103.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>103.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>165.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>0</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-31.69362182046592</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>179</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>179.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>24.02</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>24.66</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>24.9</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>96.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>139</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>197.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>0</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-38.0726789817748</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>96</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>24.06</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>24.72</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>24.95</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>24.95</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>24.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>144</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>219.7</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>0</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-36.93302210572406</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>24</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>24.1</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>25</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>192.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>207.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>207.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>219.8</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>0</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-26.27161863616149</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>192</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>192.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>82.08000000000001</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>83.56</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>84.52</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>84.52</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>8934076.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>9994429.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>9994429.800000001</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>16635314.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>12031598.12</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>12031598.12</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-786354.819931291</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>8934076</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>8934076.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>81.86</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>83.68</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>83.68000000000001</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>12153145.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>12000017.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>12000017.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>17119698.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>12440671.2</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>12440671.2</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-363491.0352426264</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>12153145</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>12153145.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>81.8</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>83.84</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>84.67</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>83.84</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>84.67</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>6263654.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>18832921.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>18832921.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>18192826.1</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>12623734.72</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>12623734.72</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-91318.34157158434</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>6263654</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>6263654.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>81.94</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>83.97</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>84.72</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>83.97</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>84.72</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>11703124.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>23071327.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>23071327</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>21658616.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>13253571.02</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>13253571.02</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>931778.0544431731</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>11703124</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>11703124.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>82.3</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>84.12</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>84.85</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>84.84999999999999</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>10918150.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>23204179.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>23204179.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>21991501.9</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>13334299.3</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>13334299.3</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>1777266.189662714</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>10918150</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>10918150.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>82.67999999999999</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>84.28</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>84.28</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>84.98</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>18962016.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>23276198.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>23276198.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>21442663.0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>13462034.94</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>13462034.94</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>3005736.947488394</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>18962016</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>18962016.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>83.2</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>84.46</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>85.12</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>85.12</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>46317663.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>22239379.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>22239379</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>20288078.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>13443275.9</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>13443275.9</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>3791504.639114775</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>46317663</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>46317663.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>83.58</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>84.64</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>85.25</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>84.64</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>85.25</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>27455682.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>17552730.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>17552730.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>16562872.1</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>12829799.08</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>12829799.08</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>1847656.854326935</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>27455682</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>27455682.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>83.74000000000001</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>84.74</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>85.33</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>84.73999999999999</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>85.33</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>12367386.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>20245906.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>20245906.8</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>14605958.4</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>12474888.6</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>12474888.6</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>1025670.238404058</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>12367386</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>12367386.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>84.02</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>84.8</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>85.4</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>85.40000000000001</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>11278247.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>20778824.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>20778824.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>13975022.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>12447055.32</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>12447055.32</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>1431375.70714266</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>11278247</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>11278247.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,21 +24277,17 @@
           <t>84.36</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>84.85</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
+      <c r="AM56" t="n">
+        <v>84.84999999999999</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>85.47</v>
+      </c>
+      <c r="AO56" t="inlineStr">
         <is>
           <t>85.47</t>
         </is>
       </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>85.47</t>
-        </is>
-      </c>
       <c r="AP56" t="inlineStr">
         <is>
           <t>-64.04</t>
@@ -24656,20 +24328,16 @@
           <t>13777917.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>19609127.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>19609127.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>13938455.4</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>12418863.26</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>12418863.26</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>2076527.851514142</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>13777917</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>13777917.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
